--- a/AI_Predictor/NonPregnant_Recommended_AI.xlsx
+++ b/AI_Predictor/NonPregnant_Recommended_AI.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,30 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>Prev_AI_Success_Rate</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Past_AI_Success_Rate</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Days_Since_Last_Estrus</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Pregnancy_Prob_Today</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Time_to_Pregnancy</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Recommended_Next_AI</t>
         </is>
@@ -669,12 +684,21 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1927941739559174</v>
+        <v>0.5</v>
       </c>
       <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.09484589844942093</v>
+      </c>
+      <c r="AE2" t="n">
         <v>-310</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AF2" s="2" t="n">
         <v>45958</v>
       </c>
     </row>
@@ -768,13 +792,22 @@
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01320690289139748</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.01275877933949232</v>
+      </c>
+      <c r="AE3" t="n">
         <v>-310</v>
       </c>
-      <c r="AC3" s="2" t="n">
-        <v>46101</v>
+      <c r="AF3" s="2" t="n">
+        <v>46108</v>
       </c>
     </row>
     <row r="4">
@@ -867,12 +900,21 @@
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01186839397996664</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.01085075177252293</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-310</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AF4" s="2" t="n">
         <v>46063</v>
       </c>
     </row>
@@ -966,13 +1008,22 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2853825092315674</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>364</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1242156997323036</v>
+      </c>
+      <c r="AE5" t="n">
         <v>-310</v>
       </c>
-      <c r="AC5" s="2" t="n">
-        <v>45982</v>
+      <c r="AF5" s="2" t="n">
+        <v>46027</v>
       </c>
     </row>
     <row r="6">
@@ -1065,12 +1116,21 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02547437511384487</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>246</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0242614857852459</v>
+      </c>
+      <c r="AE6" t="n">
         <v>-310</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -1164,13 +1224,22 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01104799099266529</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>338</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.01231988426297903</v>
+      </c>
+      <c r="AE7" t="n">
         <v>-250</v>
       </c>
-      <c r="AC7" s="2" t="n">
-        <v>46075</v>
+      <c r="AF7" s="2" t="n">
+        <v>46074</v>
       </c>
     </row>
     <row r="8">
@@ -1263,13 +1332,22 @@
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01302983798086643</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-145</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.01603587158024311</v>
+      </c>
+      <c r="AE8" t="n">
         <v>-310</v>
       </c>
-      <c r="AC8" s="2" t="n">
-        <v>46040</v>
+      <c r="AF8" s="2" t="n">
+        <v>46068</v>
       </c>
     </row>
     <row r="9">
@@ -1362,12 +1440,21 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03602215647697449</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.03182863816618919</v>
+      </c>
+      <c r="AE9" t="n">
         <v>-280</v>
       </c>
-      <c r="AC9" s="2" t="n">
+      <c r="AF9" s="2" t="n">
         <v>46078</v>
       </c>
     </row>
@@ -1461,12 +1548,21 @@
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01559321768581867</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.02461682632565498</v>
+      </c>
+      <c r="AE10" t="n">
         <v>-310</v>
       </c>
-      <c r="AC10" s="2" t="n">
+      <c r="AF10" s="2" t="n">
         <v>46101</v>
       </c>
     </row>
@@ -1560,12 +1656,21 @@
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009399882517755032</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-217</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.008756519295275211</v>
+      </c>
+      <c r="AE11" t="n">
         <v>-457</v>
       </c>
-      <c r="AC11" s="2" t="n">
+      <c r="AF11" s="2" t="n">
         <v>46048</v>
       </c>
     </row>
@@ -1659,12 +1764,21 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.006959532853215933</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>136</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0123029537498951</v>
+      </c>
+      <c r="AE12" t="n">
         <v>-310</v>
       </c>
-      <c r="AC12" s="2" t="n">
+      <c r="AF12" s="2" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -1758,12 +1872,21 @@
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0326421931385994</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.04015374183654785</v>
+      </c>
+      <c r="AE13" t="n">
         <v>-310</v>
       </c>
-      <c r="AC13" s="2" t="n">
+      <c r="AF13" s="2" t="n">
         <v>46108</v>
       </c>
     </row>
@@ -1857,12 +1980,21 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01580795645713806</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.02018091641366482</v>
+      </c>
+      <c r="AE14" t="n">
         <v>-310</v>
       </c>
-      <c r="AC14" s="2" t="n">
+      <c r="AF14" s="2" t="n">
         <v>46101</v>
       </c>
     </row>
@@ -1956,13 +2088,22 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03926850855350494</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.04081177711486816</v>
+      </c>
+      <c r="AE15" t="n">
         <v>-310</v>
       </c>
-      <c r="AC15" s="2" t="n">
-        <v>46104</v>
+      <c r="AF15" s="2" t="n">
+        <v>46111</v>
       </c>
     </row>
     <row r="16">
@@ -2055,13 +2196,22 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.008864532224833965</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-88</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.01333981286734343</v>
+      </c>
+      <c r="AE16" t="n">
         <v>-310</v>
       </c>
-      <c r="AC16" s="2" t="n">
-        <v>46080</v>
+      <c r="AF16" s="2" t="n">
+        <v>46103</v>
       </c>
     </row>
     <row r="17">
@@ -2154,13 +2304,22 @@
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.02446932159364223</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-105</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.01098550204187632</v>
+      </c>
+      <c r="AE17" t="n">
         <v>-310</v>
       </c>
-      <c r="AC17" s="2" t="n">
-        <v>46081</v>
+      <c r="AF17" s="2" t="n">
+        <v>46104</v>
       </c>
     </row>
     <row r="18">
@@ -2251,12 +2410,21 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.02086658030748367</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.01182522159069777</v>
+      </c>
+      <c r="AE18" t="n">
         <v>-310</v>
       </c>
-      <c r="AC18" s="2" t="n">
+      <c r="AF18" s="2" t="n">
         <v>46111</v>
       </c>
     </row>
@@ -2348,12 +2516,21 @@
         <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.02283413894474506</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.01805827207863331</v>
+      </c>
+      <c r="AE19" t="n">
         <v>-310</v>
       </c>
-      <c r="AC19" s="2" t="n">
+      <c r="AF19" s="2" t="n">
         <v>46110</v>
       </c>
     </row>
@@ -2445,13 +2622,22 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.004685848485678434</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-220</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.00399375194683671</v>
+      </c>
+      <c r="AE20" t="n">
         <v>-310</v>
       </c>
-      <c r="AC20" s="2" t="n">
-        <v>46064</v>
+      <c r="AF20" s="2" t="n">
+        <v>46066</v>
       </c>
     </row>
     <row r="21">
@@ -2542,13 +2728,22 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.001106284093111753</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.001767331850714982</v>
+      </c>
+      <c r="AE21" t="n">
         <v>-310</v>
       </c>
-      <c r="AC21" s="2" t="n">
-        <v>45997</v>
+      <c r="AF21" s="2" t="n">
+        <v>46012</v>
       </c>
     </row>
     <row r="22">
@@ -2639,13 +2834,22 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.01407839264720678</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-182</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.01600437052547932</v>
+      </c>
+      <c r="AE22" t="n">
         <v>-310</v>
       </c>
-      <c r="AC22" s="2" t="n">
-        <v>45982</v>
+      <c r="AF22" s="2" t="n">
+        <v>45997</v>
       </c>
     </row>
     <row r="23">
@@ -2736,13 +2940,22 @@
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.03268440067768097</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>294</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.02177087217569351</v>
+      </c>
+      <c r="AE23" t="n">
         <v>-310</v>
       </c>
-      <c r="AC23" s="2" t="n">
-        <v>46050</v>
+      <c r="AF23" s="2" t="n">
+        <v>46067</v>
       </c>
     </row>
     <row r="24">
@@ -2833,12 +3046,21 @@
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.04433642700314522</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>175</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.02098115906119347</v>
+      </c>
+      <c r="AE24" t="n">
         <v>-310</v>
       </c>
-      <c r="AC24" s="2" t="n">
+      <c r="AF24" s="2" t="n">
         <v>46049</v>
       </c>
     </row>
@@ -2930,13 +3152,22 @@
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0107177970930934</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-107</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.01368913613259792</v>
+      </c>
+      <c r="AE25" t="n">
         <v>-310</v>
       </c>
-      <c r="AC25" s="2" t="n">
-        <v>45996</v>
+      <c r="AF25" s="2" t="n">
+        <v>46011</v>
       </c>
     </row>
     <row r="26">
@@ -3025,12 +3256,21 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01515156216919422</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>267</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.005619226489216089</v>
+      </c>
+      <c r="AE26" t="n">
         <v>-280</v>
       </c>
-      <c r="AC26" s="2" t="n">
+      <c r="AF26" s="2" t="n">
         <v>46035</v>
       </c>
     </row>
@@ -3124,13 +3364,22 @@
         <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.003035606117919087</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.005664837546646595</v>
+      </c>
+      <c r="AE27" t="n">
         <v>-310</v>
       </c>
-      <c r="AC27" s="2" t="n">
-        <v>45982</v>
+      <c r="AF27" s="2" t="n">
+        <v>45995</v>
       </c>
     </row>
     <row r="28">
@@ -3221,13 +3470,22 @@
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.008958536200225353</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.01391637418419123</v>
+      </c>
+      <c r="AE28" t="n">
         <v>-310</v>
       </c>
-      <c r="AC28" s="2" t="n">
-        <v>45996</v>
+      <c r="AF28" s="2" t="n">
+        <v>46011</v>
       </c>
     </row>
     <row r="29">
@@ -3320,13 +3578,22 @@
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.05264005437493324</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-96</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.04590364173054695</v>
+      </c>
+      <c r="AE29" t="n">
         <v>-310</v>
       </c>
-      <c r="AC29" s="2" t="n">
-        <v>46012</v>
+      <c r="AF29" s="2" t="n">
+        <v>46035</v>
       </c>
     </row>
     <row r="30">
@@ -3417,13 +3684,22 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.004094794392585754</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-217</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.003758405102416873</v>
+      </c>
+      <c r="AE30" t="n">
         <v>-388</v>
       </c>
-      <c r="AC30" s="2" t="n">
-        <v>45967</v>
+      <c r="AF30" s="2" t="n">
+        <v>45982</v>
       </c>
     </row>
     <row r="31">
@@ -3516,13 +3792,22 @@
         <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.003092325292527676</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.00313809490762651</v>
+      </c>
+      <c r="AE31" t="n">
         <v>-310</v>
       </c>
-      <c r="AC31" s="2" t="n">
-        <v>46011</v>
+      <c r="AF31" s="2" t="n">
+        <v>46034</v>
       </c>
     </row>
     <row r="32">
@@ -3613,12 +3898,21 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.01284161116927862</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.01784081570804119</v>
+      </c>
+      <c r="AE32" t="n">
         <v>-310</v>
       </c>
-      <c r="AC32" s="2" t="n">
+      <c r="AF32" s="2" t="n">
         <v>46039</v>
       </c>
     </row>
@@ -3708,13 +4002,22 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04652461782097816</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.02202130854129791</v>
+      </c>
+      <c r="AE33" t="n">
         <v>-310</v>
       </c>
-      <c r="AC33" s="2" t="n">
-        <v>45859</v>
+      <c r="AF33" s="2" t="n">
+        <v>45874</v>
       </c>
     </row>
     <row r="34">
@@ -3805,12 +4108,21 @@
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.03180685266852379</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>153</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.03611398488283157</v>
+      </c>
+      <c r="AE34" t="n">
         <v>-310</v>
       </c>
-      <c r="AC34" s="2" t="n">
+      <c r="AF34" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -3902,12 +4214,21 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1618706732988358</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>769</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.2675143778324127</v>
+      </c>
+      <c r="AE35" t="n">
         <v>-280</v>
       </c>
-      <c r="AC35" s="2" t="n">
+      <c r="AF35" s="2" t="n">
         <v>46070</v>
       </c>
     </row>
@@ -3999,13 +4320,22 @@
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.2285545915365219</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>766</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.1843936592340469</v>
+      </c>
+      <c r="AE36" t="n">
         <v>-280</v>
       </c>
-      <c r="AC36" s="2" t="n">
-        <v>46070</v>
+      <c r="AF36" s="2" t="n">
+        <v>46072</v>
       </c>
     </row>
     <row r="37">
@@ -4096,12 +4426,21 @@
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.03485270962119102</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>174</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.03168809041380882</v>
+      </c>
+      <c r="AE37" t="n">
         <v>-310</v>
       </c>
-      <c r="AC37" s="2" t="n">
+      <c r="AF37" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -4191,12 +4530,21 @@
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.0103106452152133</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>152</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.0136669036000967</v>
+      </c>
+      <c r="AE38" t="n">
         <v>-310</v>
       </c>
-      <c r="AC38" s="2" t="n">
+      <c r="AF38" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4286,12 +4634,21 @@
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.03506767749786377</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>178</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.0251748338341713</v>
+      </c>
+      <c r="AE39" t="n">
         <v>-310</v>
       </c>
-      <c r="AC39" s="2" t="n">
+      <c r="AF39" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -4381,12 +4738,21 @@
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.007065230049192905</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>152</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.005532855167984962</v>
+      </c>
+      <c r="AE40" t="n">
         <v>-310</v>
       </c>
-      <c r="AC40" s="2" t="n">
+      <c r="AF40" s="2" t="n">
         <v>45859</v>
       </c>
     </row>
@@ -4476,12 +4842,21 @@
         <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.0166716743260622</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>152</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.01463919598609209</v>
+      </c>
+      <c r="AE41" t="n">
         <v>-310</v>
       </c>
-      <c r="AC41" s="2" t="n">
+      <c r="AF41" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4573,12 +4948,21 @@
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.03513773903250694</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>169</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.02160077728331089</v>
+      </c>
+      <c r="AE42" t="n">
         <v>-310</v>
       </c>
-      <c r="AC42" s="2" t="n">
+      <c r="AF42" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -4668,12 +5052,21 @@
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.01110380887985229</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.007437913678586483</v>
+      </c>
+      <c r="AE43" t="n">
         <v>-310</v>
       </c>
-      <c r="AC43" s="2" t="n">
+      <c r="AF43" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4763,13 +5156,22 @@
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.2018447816371918</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>351</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.1355659067630768</v>
+      </c>
+      <c r="AE44" t="n">
         <v>-310</v>
       </c>
-      <c r="AC44" s="2" t="n">
-        <v>45904</v>
+      <c r="AF44" s="2" t="n">
+        <v>45919</v>
       </c>
     </row>
     <row r="45">
@@ -4858,12 +5260,21 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.05452451109886169</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>105</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.06999573856592178</v>
+      </c>
+      <c r="AE45" t="n">
         <v>-310</v>
       </c>
-      <c r="AC45" s="2" t="n">
+      <c r="AF45" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4953,12 +5364,21 @@
         <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.00852481834590435</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.006897106766700745</v>
+      </c>
+      <c r="AE46" t="n">
         <v>-310</v>
       </c>
-      <c r="AC46" s="2" t="n">
+      <c r="AF46" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -5048,12 +5468,21 @@
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01592761836946011</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>146</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.03393170982599258</v>
+      </c>
+      <c r="AE47" t="n">
         <v>-310</v>
       </c>
-      <c r="AC47" s="2" t="n">
+      <c r="AF47" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -5145,12 +5574,21 @@
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.002474990673363209</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.003069066442549229</v>
+      </c>
+      <c r="AE48" t="n">
         <v>-310</v>
       </c>
-      <c r="AC48" s="2" t="n">
+      <c r="AF48" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -5244,13 +5682,22 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.02838589809834957</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.03857767954468727</v>
+      </c>
+      <c r="AE49" t="n">
         <v>-265</v>
       </c>
-      <c r="AC49" s="2" t="n">
-        <v>45908</v>
+      <c r="AF49" s="2" t="n">
+        <v>45915</v>
       </c>
     </row>
     <row r="50">
@@ -5343,13 +5790,22 @@
         <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.02235817164182663</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>646</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.03009222261607647</v>
+      </c>
+      <c r="AE50" t="n">
         <v>-310</v>
       </c>
-      <c r="AC50" s="2" t="n">
-        <v>45985</v>
+      <c r="AF50" s="2" t="n">
+        <v>46016</v>
       </c>
     </row>
     <row r="51">
@@ -5440,12 +5896,21 @@
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.1768265813589096</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.09102967381477356</v>
+      </c>
+      <c r="AE51" t="n">
         <v>-310</v>
       </c>
-      <c r="AC51" s="2" t="n">
+      <c r="AF51" s="2" t="n">
         <v>45955</v>
       </c>
     </row>
@@ -5539,12 +6004,21 @@
         <v>2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.11070666462183</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>291</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.09043868631124496</v>
+      </c>
+      <c r="AE52" t="n">
         <v>-310</v>
       </c>
-      <c r="AC52" s="2" t="n">
+      <c r="AF52" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -5636,13 +6110,22 @@
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.9536449313163757</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.9143208861351013</v>
+      </c>
+      <c r="AE53" t="n">
         <v>-220</v>
       </c>
-      <c r="AC53" s="2" t="n">
-        <v>45708</v>
+      <c r="AF53" s="2" t="n">
+        <v>45723</v>
       </c>
     </row>
     <row r="54">
@@ -5733,12 +6216,21 @@
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.02995717152953148</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>163</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.009031624533236027</v>
+      </c>
+      <c r="AE54" t="n">
         <v>-310</v>
       </c>
-      <c r="AC54" s="2" t="n">
+      <c r="AF54" s="2" t="n">
         <v>45958</v>
       </c>
     </row>
@@ -5830,12 +6322,21 @@
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.3315177857875824</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.2032688707113266</v>
+      </c>
+      <c r="AE55" t="n">
         <v>-310</v>
       </c>
-      <c r="AC55" s="2" t="n">
+      <c r="AF55" s="2" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -5927,12 +6428,21 @@
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.03007326647639275</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.03248533979058266</v>
+      </c>
+      <c r="AE56" t="n">
         <v>-280</v>
       </c>
-      <c r="AC56" s="2" t="n">
+      <c r="AF56" s="2" t="n">
         <v>45738</v>
       </c>
     </row>
@@ -6024,12 +6534,21 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01864475943148136</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>146</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.007090762723237276</v>
+      </c>
+      <c r="AE57" t="n">
         <v>-220</v>
       </c>
-      <c r="AC57" s="2" t="n">
+      <c r="AF57" s="2" t="n">
         <v>45882</v>
       </c>
     </row>
@@ -6121,12 +6640,21 @@
         <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.009192395024001598</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.01194341108202934</v>
+      </c>
+      <c r="AE58" t="n">
         <v>-310</v>
       </c>
-      <c r="AC58" s="2" t="n">
+      <c r="AF58" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6220,13 +6748,22 @@
         <v>2</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03585891053080559</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.03755462542176247</v>
+      </c>
+      <c r="AE59" t="n">
         <v>-310</v>
       </c>
-      <c r="AC59" s="2" t="n">
-        <v>45783</v>
+      <c r="AF59" s="2" t="n">
+        <v>45798</v>
       </c>
     </row>
     <row r="60">
@@ -6317,12 +6854,21 @@
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.02167799323797226</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.02642197906970978</v>
+      </c>
+      <c r="AE60" t="n">
         <v>-297</v>
       </c>
-      <c r="AC60" s="2" t="n">
+      <c r="AF60" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6416,12 +6962,21 @@
         <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.003173880511894822</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.01040103286504745</v>
+      </c>
+      <c r="AE61" t="n">
         <v>-310</v>
       </c>
-      <c r="AC61" s="2" t="n">
+      <c r="AF61" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6513,13 +7068,22 @@
         <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.02926869690418243</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.01349372323602438</v>
+      </c>
+      <c r="AE62" t="n">
         <v>-310</v>
       </c>
-      <c r="AC62" s="2" t="n">
-        <v>45921</v>
+      <c r="AF62" s="2" t="n">
+        <v>45951</v>
       </c>
     </row>
     <row r="63">
@@ -6610,12 +7174,21 @@
         <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.0089173698797822</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.01118039805442095</v>
+      </c>
+      <c r="AE63" t="n">
         <v>-310</v>
       </c>
-      <c r="AC63" s="2" t="n">
+      <c r="AF63" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6709,13 +7282,22 @@
         <v>1</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.2631850838661194</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.1216617673635483</v>
+      </c>
+      <c r="AE64" t="n">
         <v>-310</v>
       </c>
-      <c r="AC64" s="2" t="n">
-        <v>45903</v>
+      <c r="AF64" s="2" t="n">
+        <v>45918</v>
       </c>
     </row>
     <row r="65">
@@ -6808,12 +7390,21 @@
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.004349960945546627</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.003875332185998559</v>
+      </c>
+      <c r="AE65" t="n">
         <v>-310</v>
       </c>
-      <c r="AC65" s="2" t="n">
+      <c r="AF65" s="2" t="n">
         <v>45783</v>
       </c>
     </row>
@@ -6905,12 +7496,21 @@
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.04500741511583328</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.05354776605963707</v>
+      </c>
+      <c r="AE66" t="n">
         <v>-310</v>
       </c>
-      <c r="AC66" s="2" t="n">
+      <c r="AF66" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7002,12 +7602,21 @@
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.03027279116213322</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.02591319009661674</v>
+      </c>
+      <c r="AE67" t="n">
         <v>-310</v>
       </c>
-      <c r="AC67" s="2" t="n">
+      <c r="AF67" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7099,13 +7708,22 @@
         <v>1</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.3193719387054443</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>359</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.1915939599275589</v>
+      </c>
+      <c r="AE68" t="n">
         <v>-310</v>
       </c>
-      <c r="AC68" s="2" t="n">
-        <v>45901</v>
+      <c r="AF68" s="2" t="n">
+        <v>45903</v>
       </c>
     </row>
     <row r="69">
@@ -7196,13 +7814,22 @@
         <v>1</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01045467238873243</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.009199511259794235</v>
+      </c>
+      <c r="AE69" t="n">
         <v>-310</v>
       </c>
-      <c r="AC69" s="2" t="n">
-        <v>45798</v>
+      <c r="AF69" s="2" t="n">
+        <v>45813</v>
       </c>
     </row>
     <row r="70">
@@ -7295,12 +7922,21 @@
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01833918131887913</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.02402550168335438</v>
+      </c>
+      <c r="AE70" t="n">
         <v>-310</v>
       </c>
-      <c r="AC70" s="2" t="n">
+      <c r="AF70" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7392,12 +8028,21 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.008834823966026306</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.007090866565704346</v>
+      </c>
+      <c r="AE71" t="n">
         <v>-310</v>
       </c>
-      <c r="AC71" s="2" t="n">
+      <c r="AF71" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7491,13 +8136,22 @@
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.007175135891884565</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.003820785088464618</v>
+      </c>
+      <c r="AE72" t="n">
         <v>-205</v>
       </c>
-      <c r="AC72" s="2" t="n">
-        <v>45798</v>
+      <c r="AF72" s="2" t="n">
+        <v>45800</v>
       </c>
     </row>
     <row r="73">
@@ -7588,12 +8242,21 @@
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.006032895762473345</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.008872806094586849</v>
+      </c>
+      <c r="AE73" t="n">
         <v>-310</v>
       </c>
-      <c r="AC73" s="2" t="n">
+      <c r="AF73" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7685,12 +8348,21 @@
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.2613018751144409</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.1942048966884613</v>
+      </c>
+      <c r="AE74" t="n">
         <v>-310</v>
       </c>
-      <c r="AC74" s="2" t="n">
+      <c r="AF74" s="2" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -7784,12 +8456,21 @@
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.1115086451172829</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1453</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1409570574760437</v>
+      </c>
+      <c r="AE75" t="n">
         <v>1173</v>
       </c>
-      <c r="AC75" s="2" t="n">
+      <c r="AF75" s="2" t="n">
         <v>45711</v>
       </c>
     </row>
@@ -7883,12 +8564,21 @@
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.5433034300804138</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.6690725088119507</v>
+      </c>
+      <c r="AE76" t="n">
         <v>718</v>
       </c>
-      <c r="AC76" s="2" t="n">
+      <c r="AF76" s="2" t="n">
         <v>45806</v>
       </c>
     </row>
@@ -7982,13 +8672,22 @@
         <v>2</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.2228798419237137</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>381</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0.1992234587669373</v>
+      </c>
+      <c r="AE77" t="n">
         <v>101</v>
       </c>
-      <c r="AC77" s="2" t="n">
-        <v>45085</v>
+      <c r="AF77" s="2" t="n">
+        <v>45105</v>
       </c>
     </row>
     <row r="78">
@@ -8079,12 +8778,21 @@
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.1362634003162384</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>375</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0.09268827736377716</v>
+      </c>
+      <c r="AE78" t="n">
         <v>95</v>
       </c>
-      <c r="AC78" s="2" t="n">
+      <c r="AF78" s="2" t="n">
         <v>45114</v>
       </c>
     </row>
@@ -8178,12 +8886,21 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.2035242319107056</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>282</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0.2408418953418732</v>
+      </c>
+      <c r="AE79" t="n">
         <v>2</v>
       </c>
-      <c r="AC79" s="2" t="n">
+      <c r="AF79" s="2" t="n">
         <v>45176</v>
       </c>
     </row>
@@ -8275,12 +8992,21 @@
         <v>1</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.2514014542102814</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>261</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0.2225157767534256</v>
+      </c>
+      <c r="AE80" t="n">
         <v>-39</v>
       </c>
-      <c r="AC80" s="2" t="n">
+      <c r="AF80" s="2" t="n">
         <v>45219</v>
       </c>
     </row>
@@ -8372,12 +9098,21 @@
         <v>1</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.2563945353031158</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>247</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0.2749627530574799</v>
+      </c>
+      <c r="AE81" t="n">
         <v>-45</v>
       </c>
-      <c r="AC81" s="2" t="n">
+      <c r="AF81" s="2" t="n">
         <v>45225</v>
       </c>
     </row>
@@ -8471,12 +9206,21 @@
         <v>1</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.3285784721374512</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>222</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0.2558905482292175</v>
+      </c>
+      <c r="AE82" t="n">
         <v>-62</v>
       </c>
-      <c r="AC82" s="2" t="n">
+      <c r="AF82" s="2" t="n">
         <v>45238</v>
       </c>
     </row>
@@ -8568,12 +9312,21 @@
         <v>1</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.03220456466078758</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>182</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0.03864405304193497</v>
+      </c>
+      <c r="AE83" t="n">
         <v>-118</v>
       </c>
-      <c r="AC83" s="2" t="n">
+      <c r="AF83" s="2" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -8667,13 +9420,22 @@
         <v>3</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.03470739349722862</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>179</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0.04470883682370186</v>
+      </c>
+      <c r="AE84" t="n">
         <v>-121</v>
       </c>
-      <c r="AC84" s="2" t="n">
-        <v>45316</v>
+      <c r="AF84" s="2" t="n">
+        <v>45400</v>
       </c>
     </row>
     <row r="85">
@@ -8764,12 +9526,21 @@
         <v>1</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.06945592910051346</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>178</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0.03920075297355652</v>
+      </c>
+      <c r="AE85" t="n">
         <v>-122</v>
       </c>
-      <c r="AC85" s="2" t="n">
+      <c r="AF85" s="2" t="n">
         <v>45296</v>
       </c>
     </row>
@@ -8863,12 +9634,21 @@
         <v>1</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.0140592698007822</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>172</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0.01146524026989937</v>
+      </c>
+      <c r="AE86" t="n">
         <v>-128</v>
       </c>
-      <c r="AC86" s="2" t="n">
+      <c r="AF86" s="2" t="n">
         <v>45304</v>
       </c>
     </row>
@@ -8960,12 +9740,21 @@
         <v>1</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.08282041549682617</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>172</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.08621419221162796</v>
+      </c>
+      <c r="AE87" t="n">
         <v>-128</v>
       </c>
-      <c r="AC87" s="2" t="n">
+      <c r="AF87" s="2" t="n">
         <v>45302</v>
       </c>
     </row>
@@ -9059,12 +9848,21 @@
         <v>3</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.007500682026147842</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>153</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0.004396884702146053</v>
+      </c>
+      <c r="AE88" t="n">
         <v>-86</v>
       </c>
-      <c r="AC88" s="2" t="n">
+      <c r="AF88" s="2" t="n">
         <v>45266</v>
       </c>
     </row>
@@ -9158,12 +9956,21 @@
         <v>1</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.005561616737395525</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>150</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0.002825111616402864</v>
+      </c>
+      <c r="AE89" t="n">
         <v>-89</v>
       </c>
-      <c r="AC89" s="2" t="n">
+      <c r="AF89" s="2" t="n">
         <v>45265</v>
       </c>
     </row>
@@ -9257,12 +10064,21 @@
         <v>1</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.00570334866642952</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>149</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0.00390627421438694</v>
+      </c>
+      <c r="AE90" t="n">
         <v>-90</v>
       </c>
-      <c r="AC90" s="2" t="n">
+      <c r="AF90" s="2" t="n">
         <v>45267</v>
       </c>
     </row>
@@ -9354,12 +10170,21 @@
         <v>1</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.01276509929448366</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>139</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0.009338484145700932</v>
+      </c>
+      <c r="AE91" t="n">
         <v>-130</v>
       </c>
-      <c r="AC91" s="2" t="n">
+      <c r="AF91" s="2" t="n">
         <v>45304</v>
       </c>
     </row>
@@ -9451,12 +10276,21 @@
         <v>1</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.0175168514251709</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>128</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0.01252417452633381</v>
+      </c>
+      <c r="AE92" t="n">
         <v>-141</v>
       </c>
-      <c r="AC92" s="2" t="n">
+      <c r="AF92" s="2" t="n">
         <v>45315</v>
       </c>
     </row>
@@ -9548,12 +10382,21 @@
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.009302081540226936</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>128</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0.00579608790576458</v>
+      </c>
+      <c r="AE93" t="n">
         <v>-141</v>
       </c>
-      <c r="AC93" s="2" t="n">
+      <c r="AF93" s="2" t="n">
         <v>45317</v>
       </c>
     </row>
@@ -9645,12 +10488,21 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.02432912029325962</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>110</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0.01023478712886572</v>
+      </c>
+      <c r="AE94" t="n">
         <v>-130</v>
       </c>
-      <c r="AC94" s="2" t="n">
+      <c r="AF94" s="2" t="n">
         <v>45273</v>
       </c>
     </row>
@@ -9744,12 +10596,21 @@
         <v>1</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.006277259904891253</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>96</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0.00821247324347496</v>
+      </c>
+      <c r="AE95" t="n">
         <v>-144</v>
       </c>
-      <c r="AC95" s="2" t="n">
+      <c r="AF95" s="2" t="n">
         <v>45318</v>
       </c>
     </row>
@@ -9841,13 +10702,22 @@
         <v>1</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.01144663710147142</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>93</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0.009250856935977936</v>
+      </c>
+      <c r="AE96" t="n">
         <v>-147</v>
       </c>
-      <c r="AC96" s="2" t="n">
-        <v>45293</v>
+      <c r="AF96" s="2" t="n">
+        <v>45324</v>
       </c>
     </row>
     <row r="97">
@@ -9940,13 +10810,22 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.01784624718129635</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>92</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>0.01411768142133951</v>
+      </c>
+      <c r="AE97" t="n">
         <v>-148</v>
       </c>
-      <c r="AC97" s="2" t="n">
-        <v>45293</v>
+      <c r="AF97" s="2" t="n">
+        <v>45294</v>
       </c>
     </row>
     <row r="98">
@@ -10039,12 +10918,21 @@
         <v>1</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.009655642323195934</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>86</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0.005402962677180767</v>
+      </c>
+      <c r="AE98" t="n">
         <v>-185</v>
       </c>
-      <c r="AC98" s="2" t="n">
+      <c r="AF98" s="2" t="n">
         <v>45359</v>
       </c>
     </row>

--- a/AI_Predictor/NonPregnant_Recommended_AI.xlsx
+++ b/AI_Predictor/NonPregnant_Recommended_AI.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,30 +565,20 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Prev_AI_Success_Rate</t>
+          <t>Days_Since_Last_Estrus</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Past_AI_Success_Rate</t>
+          <t>Pregnancy_Prob_Today</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Days_Since_Last_Estrus</t>
+          <t>Time_to_Pregnancy</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Pregnancy_Prob_Today</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Time_to_Pregnancy</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Recommended_Next_AI</t>
         </is>
@@ -684,21 +674,15 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>0.100779689848423</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.09484589844942093</v>
-      </c>
-      <c r="AE2" t="n">
         <v>-310</v>
       </c>
-      <c r="AF2" s="2" t="n">
+      <c r="AD2" s="2" t="n">
         <v>45958</v>
       </c>
     </row>
@@ -792,22 +776,16 @@
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3333333333333333</v>
+        <v>-6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.01269085984677076</v>
       </c>
       <c r="AC3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.01275877933949232</v>
-      </c>
-      <c r="AE3" t="n">
         <v>-310</v>
       </c>
-      <c r="AF3" s="2" t="n">
-        <v>46108</v>
+      <c r="AD3" s="2" t="n">
+        <v>46101</v>
       </c>
     </row>
     <row r="4">
@@ -900,21 +878,15 @@
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3333333333333333</v>
+        <v>-42</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.01276877801865339</v>
       </c>
       <c r="AC4" t="n">
-        <v>-42</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.01085075177252293</v>
-      </c>
-      <c r="AE4" t="n">
         <v>-310</v>
       </c>
-      <c r="AF4" s="2" t="n">
+      <c r="AD4" s="2" t="n">
         <v>46063</v>
       </c>
     </row>
@@ -1008,22 +980,16 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.1201586648821831</v>
       </c>
       <c r="AC5" t="n">
-        <v>364</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.1242156997323036</v>
-      </c>
-      <c r="AE5" t="n">
         <v>-310</v>
       </c>
-      <c r="AF5" s="2" t="n">
-        <v>46027</v>
+      <c r="AD5" s="2" t="n">
+        <v>45967</v>
       </c>
     </row>
     <row r="6">
@@ -1116,21 +1082,15 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.02081024646759033</v>
       </c>
       <c r="AC6" t="n">
-        <v>246</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0242614857852459</v>
-      </c>
-      <c r="AE6" t="n">
         <v>-310</v>
       </c>
-      <c r="AF6" s="2" t="n">
+      <c r="AD6" s="2" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -1224,22 +1184,16 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.01426002010703087</v>
       </c>
       <c r="AC7" t="n">
-        <v>338</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.01231988426297903</v>
-      </c>
-      <c r="AE7" t="n">
         <v>-250</v>
       </c>
-      <c r="AF7" s="2" t="n">
-        <v>46074</v>
+      <c r="AD7" s="2" t="n">
+        <v>46075</v>
       </c>
     </row>
     <row r="8">
@@ -1332,22 +1286,16 @@
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-145</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.02012930996716022</v>
       </c>
       <c r="AC8" t="n">
-        <v>-145</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.01603587158024311</v>
-      </c>
-      <c r="AE8" t="n">
         <v>-310</v>
       </c>
-      <c r="AF8" s="2" t="n">
-        <v>46068</v>
+      <c r="AD8" s="2" t="n">
+        <v>46040</v>
       </c>
     </row>
     <row r="9">
@@ -1440,22 +1388,16 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.03646769374608994</v>
       </c>
       <c r="AC9" t="n">
-        <v>-34</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.03182863816618919</v>
-      </c>
-      <c r="AE9" t="n">
         <v>-280</v>
       </c>
-      <c r="AF9" s="2" t="n">
-        <v>46078</v>
+      <c r="AD9" s="2" t="n">
+        <v>46071</v>
       </c>
     </row>
     <row r="10">
@@ -1548,22 +1490,16 @@
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>0.02614293619990349</v>
       </c>
       <c r="AC10" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.02461682632565498</v>
-      </c>
-      <c r="AE10" t="n">
         <v>-310</v>
       </c>
-      <c r="AF10" s="2" t="n">
-        <v>46101</v>
+      <c r="AD10" s="2" t="n">
+        <v>46078</v>
       </c>
     </row>
     <row r="11">
@@ -1656,21 +1592,15 @@
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-217</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>0.009919531643390656</v>
       </c>
       <c r="AC11" t="n">
-        <v>-217</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.008756519295275211</v>
-      </c>
-      <c r="AE11" t="n">
         <v>-457</v>
       </c>
-      <c r="AF11" s="2" t="n">
+      <c r="AD11" s="2" t="n">
         <v>46048</v>
       </c>
     </row>
@@ -1764,21 +1694,15 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.01639477163553238</v>
       </c>
       <c r="AC12" t="n">
-        <v>136</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.0123029537498951</v>
-      </c>
-      <c r="AE12" t="n">
         <v>-310</v>
       </c>
-      <c r="AF12" s="2" t="n">
+      <c r="AD12" s="2" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -1872,22 +1796,16 @@
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.04782848060131073</v>
       </c>
       <c r="AC13" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.04015374183654785</v>
-      </c>
-      <c r="AE13" t="n">
         <v>-310</v>
       </c>
-      <c r="AF13" s="2" t="n">
-        <v>46108</v>
+      <c r="AD13" s="2" t="n">
+        <v>46101</v>
       </c>
     </row>
     <row r="14">
@@ -1980,22 +1898,16 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>0.02476038783788681</v>
       </c>
       <c r="AC14" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.02018091641366482</v>
-      </c>
-      <c r="AE14" t="n">
         <v>-310</v>
       </c>
-      <c r="AF14" s="2" t="n">
-        <v>46101</v>
+      <c r="AD14" s="2" t="n">
+        <v>46078</v>
       </c>
     </row>
     <row r="15">
@@ -2088,22 +2000,16 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.05204192921519279</v>
       </c>
       <c r="AC15" t="n">
-        <v>-41</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.04081177711486816</v>
-      </c>
-      <c r="AE15" t="n">
         <v>-310</v>
       </c>
-      <c r="AF15" s="2" t="n">
-        <v>46111</v>
+      <c r="AD15" s="2" t="n">
+        <v>46104</v>
       </c>
     </row>
     <row r="16">
@@ -2196,22 +2102,16 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.01220481470227242</v>
       </c>
       <c r="AC16" t="n">
-        <v>-88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.01333981286734343</v>
-      </c>
-      <c r="AE16" t="n">
         <v>-310</v>
       </c>
-      <c r="AF16" s="2" t="n">
-        <v>46103</v>
+      <c r="AD16" s="2" t="n">
+        <v>46080</v>
       </c>
     </row>
     <row r="17">
@@ -2304,22 +2204,16 @@
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.01173723023384809</v>
       </c>
       <c r="AC17" t="n">
-        <v>-105</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.01098550204187632</v>
-      </c>
-      <c r="AE17" t="n">
         <v>-310</v>
       </c>
-      <c r="AF17" s="2" t="n">
-        <v>46104</v>
+      <c r="AD17" s="2" t="n">
+        <v>46066</v>
       </c>
     </row>
     <row r="18">
@@ -2410,21 +2304,15 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.0130463195964694</v>
       </c>
       <c r="AC18" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.01182522159069777</v>
-      </c>
-      <c r="AE18" t="n">
         <v>-310</v>
       </c>
-      <c r="AF18" s="2" t="n">
+      <c r="AD18" s="2" t="n">
         <v>46111</v>
       </c>
     </row>
@@ -2516,21 +2404,15 @@
         <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>0.01244550943374634</v>
       </c>
       <c r="AC19" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.01805827207863331</v>
-      </c>
-      <c r="AE19" t="n">
         <v>-310</v>
       </c>
-      <c r="AF19" s="2" t="n">
+      <c r="AD19" s="2" t="n">
         <v>46110</v>
       </c>
     </row>
@@ -2622,22 +2504,16 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>0.004047406371682882</v>
       </c>
       <c r="AC20" t="n">
-        <v>-220</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.00399375194683671</v>
-      </c>
-      <c r="AE20" t="n">
         <v>-310</v>
       </c>
-      <c r="AF20" s="2" t="n">
-        <v>46066</v>
+      <c r="AD20" s="2" t="n">
+        <v>46051</v>
       </c>
     </row>
     <row r="21">
@@ -2728,22 +2604,16 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>-127</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>0.002338217338547111</v>
       </c>
       <c r="AC21" t="n">
-        <v>-127</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.001767331850714982</v>
-      </c>
-      <c r="AE21" t="n">
         <v>-310</v>
       </c>
-      <c r="AF21" s="2" t="n">
-        <v>46012</v>
+      <c r="AD21" s="2" t="n">
+        <v>45995</v>
       </c>
     </row>
     <row r="22">
@@ -2834,22 +2704,16 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>-182</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>0.01411259826272726</v>
       </c>
       <c r="AC22" t="n">
-        <v>-182</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.01600437052547932</v>
-      </c>
-      <c r="AE22" t="n">
         <v>-310</v>
       </c>
-      <c r="AF22" s="2" t="n">
-        <v>45997</v>
+      <c r="AD22" s="2" t="n">
+        <v>45982</v>
       </c>
     </row>
     <row r="23">
@@ -2940,22 +2804,16 @@
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>0.01908596605062485</v>
       </c>
       <c r="AC23" t="n">
-        <v>294</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.02177087217569351</v>
-      </c>
-      <c r="AE23" t="n">
         <v>-310</v>
       </c>
-      <c r="AF23" s="2" t="n">
-        <v>46067</v>
+      <c r="AD23" s="2" t="n">
+        <v>46050</v>
       </c>
     </row>
     <row r="24">
@@ -3046,22 +2904,16 @@
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>0.01309718750417233</v>
       </c>
       <c r="AC24" t="n">
-        <v>175</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.02098115906119347</v>
-      </c>
-      <c r="AE24" t="n">
         <v>-310</v>
       </c>
-      <c r="AF24" s="2" t="n">
-        <v>46049</v>
+      <c r="AD24" s="2" t="n">
+        <v>46042</v>
       </c>
     </row>
     <row r="25">
@@ -3152,22 +3004,16 @@
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>-107</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>0.01311829499900341</v>
       </c>
       <c r="AC25" t="n">
-        <v>-107</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.01368913613259792</v>
-      </c>
-      <c r="AE25" t="n">
         <v>-310</v>
       </c>
-      <c r="AF25" s="2" t="n">
-        <v>46011</v>
+      <c r="AD25" s="2" t="n">
+        <v>45996</v>
       </c>
     </row>
     <row r="26">
@@ -3256,21 +3102,15 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>0.00626858975738287</v>
       </c>
       <c r="AC26" t="n">
-        <v>267</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.005619226489216089</v>
-      </c>
-      <c r="AE26" t="n">
         <v>-280</v>
       </c>
-      <c r="AF26" s="2" t="n">
+      <c r="AD26" s="2" t="n">
         <v>46035</v>
       </c>
     </row>
@@ -3364,22 +3204,16 @@
         <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>-213</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>0.006811540108174086</v>
       </c>
       <c r="AC27" t="n">
-        <v>-213</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.005664837546646595</v>
-      </c>
-      <c r="AE27" t="n">
         <v>-310</v>
       </c>
-      <c r="AF27" s="2" t="n">
-        <v>45995</v>
+      <c r="AD27" s="2" t="n">
+        <v>45982</v>
       </c>
     </row>
     <row r="28">
@@ -3470,22 +3304,16 @@
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>0.01320787984877825</v>
       </c>
       <c r="AC28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.01391637418419123</v>
-      </c>
-      <c r="AE28" t="n">
         <v>-310</v>
       </c>
-      <c r="AF28" s="2" t="n">
-        <v>46011</v>
+      <c r="AD28" s="2" t="n">
+        <v>45994</v>
       </c>
     </row>
     <row r="29">
@@ -3578,22 +3406,16 @@
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>0.03648063167929649</v>
       </c>
       <c r="AC29" t="n">
-        <v>-96</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.04590364173054695</v>
-      </c>
-      <c r="AE29" t="n">
         <v>-310</v>
       </c>
-      <c r="AF29" s="2" t="n">
-        <v>46035</v>
+      <c r="AD29" s="2" t="n">
+        <v>46012</v>
       </c>
     </row>
     <row r="30">
@@ -3684,22 +3506,16 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>-217</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.003893292741850019</v>
       </c>
       <c r="AC30" t="n">
-        <v>-217</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.003758405102416873</v>
-      </c>
-      <c r="AE30" t="n">
         <v>-388</v>
       </c>
-      <c r="AF30" s="2" t="n">
-        <v>45982</v>
+      <c r="AD30" s="2" t="n">
+        <v>45952</v>
       </c>
     </row>
     <row r="31">
@@ -3792,22 +3608,16 @@
         <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>-127</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>0.003587423590943217</v>
       </c>
       <c r="AC31" t="n">
-        <v>-127</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.00313809490762651</v>
-      </c>
-      <c r="AE31" t="n">
         <v>-310</v>
       </c>
-      <c r="AF31" s="2" t="n">
-        <v>46034</v>
+      <c r="AD31" s="2" t="n">
+        <v>46011</v>
       </c>
     </row>
     <row r="32">
@@ -3898,21 +3708,15 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.03060656413435936</v>
       </c>
       <c r="AC32" t="n">
-        <v>68</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.01784081570804119</v>
-      </c>
-      <c r="AE32" t="n">
         <v>-310</v>
       </c>
-      <c r="AF32" s="2" t="n">
+      <c r="AD32" s="2" t="n">
         <v>46039</v>
       </c>
     </row>
@@ -4002,22 +3806,16 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>0.02590704150497913</v>
       </c>
       <c r="AC33" t="n">
-        <v>180</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.02202130854129791</v>
-      </c>
-      <c r="AE33" t="n">
         <v>-310</v>
       </c>
-      <c r="AF33" s="2" t="n">
-        <v>45874</v>
+      <c r="AD33" s="2" t="n">
+        <v>45859</v>
       </c>
     </row>
     <row r="34">
@@ -4108,21 +3906,15 @@
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>0.03384266421198845</v>
       </c>
       <c r="AC34" t="n">
-        <v>153</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.03611398488283157</v>
-      </c>
-      <c r="AE34" t="n">
         <v>-310</v>
       </c>
-      <c r="AF34" s="2" t="n">
+      <c r="AD34" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4214,21 +4006,15 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.2659305036067963</v>
       </c>
       <c r="AC35" t="n">
-        <v>769</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.2675143778324127</v>
-      </c>
-      <c r="AE35" t="n">
         <v>-280</v>
       </c>
-      <c r="AF35" s="2" t="n">
+      <c r="AD35" s="2" t="n">
         <v>46070</v>
       </c>
     </row>
@@ -4320,22 +4106,16 @@
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.1832364648580551</v>
       </c>
       <c r="AC36" t="n">
-        <v>766</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.1843936592340469</v>
-      </c>
-      <c r="AE36" t="n">
         <v>-280</v>
       </c>
-      <c r="AF36" s="2" t="n">
-        <v>46072</v>
+      <c r="AD36" s="2" t="n">
+        <v>46070</v>
       </c>
     </row>
     <row r="37">
@@ -4426,22 +4206,16 @@
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.02313454449176788</v>
       </c>
       <c r="AC37" t="n">
-        <v>174</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.03168809041380882</v>
-      </c>
-      <c r="AE37" t="n">
         <v>-310</v>
       </c>
-      <c r="AF37" s="2" t="n">
-        <v>45889</v>
+      <c r="AD37" s="2" t="n">
+        <v>45874</v>
       </c>
     </row>
     <row r="38">
@@ -4530,22 +4304,16 @@
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.01361364219337702</v>
       </c>
       <c r="AC38" t="n">
-        <v>152</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.0136669036000967</v>
-      </c>
-      <c r="AE38" t="n">
         <v>-310</v>
       </c>
-      <c r="AF38" s="2" t="n">
-        <v>45874</v>
+      <c r="AD38" s="2" t="n">
+        <v>45859</v>
       </c>
     </row>
     <row r="39">
@@ -4634,22 +4402,16 @@
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>0.02006252855062485</v>
       </c>
       <c r="AC39" t="n">
-        <v>178</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.0251748338341713</v>
-      </c>
-      <c r="AE39" t="n">
         <v>-310</v>
       </c>
-      <c r="AF39" s="2" t="n">
-        <v>45889</v>
+      <c r="AD39" s="2" t="n">
+        <v>45874</v>
       </c>
     </row>
     <row r="40">
@@ -4738,21 +4500,15 @@
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>0.005600056611001492</v>
       </c>
       <c r="AC40" t="n">
-        <v>152</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.005532855167984962</v>
-      </c>
-      <c r="AE40" t="n">
         <v>-310</v>
       </c>
-      <c r="AF40" s="2" t="n">
+      <c r="AD40" s="2" t="n">
         <v>45859</v>
       </c>
     </row>
@@ -4842,21 +4598,15 @@
         <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.01280537433922291</v>
       </c>
       <c r="AC41" t="n">
-        <v>152</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.01463919598609209</v>
-      </c>
-      <c r="AE41" t="n">
         <v>-310</v>
       </c>
-      <c r="AF41" s="2" t="n">
+      <c r="AD41" s="2" t="n">
         <v>45874</v>
       </c>
     </row>
@@ -4948,22 +4698,16 @@
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>0.02249941974878311</v>
       </c>
       <c r="AC42" t="n">
-        <v>169</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.02160077728331089</v>
-      </c>
-      <c r="AE42" t="n">
         <v>-310</v>
       </c>
-      <c r="AF42" s="2" t="n">
-        <v>45889</v>
+      <c r="AD42" s="2" t="n">
+        <v>45874</v>
       </c>
     </row>
     <row r="43">
@@ -5052,22 +4796,16 @@
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.005924140568822622</v>
       </c>
       <c r="AC43" t="n">
-        <v>122</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.007437913678586483</v>
-      </c>
-      <c r="AE43" t="n">
         <v>-310</v>
       </c>
-      <c r="AF43" s="2" t="n">
-        <v>45874</v>
+      <c r="AD43" s="2" t="n">
+        <v>45859</v>
       </c>
     </row>
     <row r="44">
@@ -5156,22 +4894,16 @@
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>0.148629441857338</v>
       </c>
       <c r="AC44" t="n">
-        <v>351</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.1355659067630768</v>
-      </c>
-      <c r="AE44" t="n">
         <v>-310</v>
       </c>
-      <c r="AF44" s="2" t="n">
-        <v>45919</v>
+      <c r="AD44" s="2" t="n">
+        <v>45904</v>
       </c>
     </row>
     <row r="45">
@@ -5260,22 +4992,16 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.07366435974836349</v>
       </c>
       <c r="AC45" t="n">
-        <v>105</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.06999573856592178</v>
-      </c>
-      <c r="AE45" t="n">
         <v>-310</v>
       </c>
-      <c r="AF45" s="2" t="n">
-        <v>45874</v>
+      <c r="AD45" s="2" t="n">
+        <v>45859</v>
       </c>
     </row>
     <row r="46">
@@ -5364,21 +5090,15 @@
         <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>0.006299444008618593</v>
       </c>
       <c r="AC46" t="n">
-        <v>180</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.006897106766700745</v>
-      </c>
-      <c r="AE46" t="n">
         <v>-310</v>
       </c>
-      <c r="AF46" s="2" t="n">
+      <c r="AD46" s="2" t="n">
         <v>45889</v>
       </c>
     </row>
@@ -5468,22 +5188,16 @@
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>0.03360961750149727</v>
       </c>
       <c r="AC47" t="n">
-        <v>146</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.03393170982599258</v>
-      </c>
-      <c r="AE47" t="n">
         <v>-310</v>
       </c>
-      <c r="AF47" s="2" t="n">
-        <v>45889</v>
+      <c r="AD47" s="2" t="n">
+        <v>45874</v>
       </c>
     </row>
     <row r="48">
@@ -5574,21 +5288,15 @@
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>0.002639548154547811</v>
       </c>
       <c r="AC48" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.003069066442549229</v>
-      </c>
-      <c r="AE48" t="n">
         <v>-310</v>
       </c>
-      <c r="AF48" s="2" t="n">
+      <c r="AD48" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -5682,22 +5390,16 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>0.03987625613808632</v>
       </c>
       <c r="AC49" t="n">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.03857767954468727</v>
-      </c>
-      <c r="AE49" t="n">
         <v>-265</v>
       </c>
-      <c r="AF49" s="2" t="n">
-        <v>45915</v>
+      <c r="AD49" s="2" t="n">
+        <v>45908</v>
       </c>
     </row>
     <row r="50">
@@ -5790,22 +5492,16 @@
         <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>0.02641122415661812</v>
       </c>
       <c r="AC50" t="n">
-        <v>646</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.03009222261607647</v>
-      </c>
-      <c r="AE50" t="n">
         <v>-310</v>
       </c>
-      <c r="AF50" s="2" t="n">
-        <v>46016</v>
+      <c r="AD50" s="2" t="n">
+        <v>45984</v>
       </c>
     </row>
     <row r="51">
@@ -5896,22 +5592,16 @@
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>0.09588371217250824</v>
       </c>
       <c r="AC51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.09102967381477356</v>
-      </c>
-      <c r="AE51" t="n">
         <v>-310</v>
       </c>
-      <c r="AF51" s="2" t="n">
-        <v>45955</v>
+      <c r="AD51" s="2" t="n">
+        <v>45948</v>
       </c>
     </row>
     <row r="52">
@@ -6004,21 +5694,15 @@
         <v>2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.0847141221165657</v>
       </c>
       <c r="AC52" t="n">
-        <v>291</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.09043868631124496</v>
-      </c>
-      <c r="AE52" t="n">
         <v>-310</v>
       </c>
-      <c r="AF52" s="2" t="n">
+      <c r="AD52" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6110,22 +5794,16 @@
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>0.8762158155441284</v>
       </c>
       <c r="AC53" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0.9143208861351013</v>
-      </c>
-      <c r="AE53" t="n">
         <v>-220</v>
       </c>
-      <c r="AF53" s="2" t="n">
-        <v>45723</v>
+      <c r="AD53" s="2" t="n">
+        <v>45708</v>
       </c>
     </row>
     <row r="54">
@@ -6216,21 +5894,15 @@
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>0.009599713608622551</v>
       </c>
       <c r="AC54" t="n">
-        <v>163</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0.009031624533236027</v>
-      </c>
-      <c r="AE54" t="n">
         <v>-310</v>
       </c>
-      <c r="AF54" s="2" t="n">
+      <c r="AD54" s="2" t="n">
         <v>45958</v>
       </c>
     </row>
@@ -6322,21 +5994,15 @@
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>0.191808670759201</v>
       </c>
       <c r="AC55" t="n">
-        <v>63</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0.2032688707113266</v>
-      </c>
-      <c r="AE55" t="n">
         <v>-310</v>
       </c>
-      <c r="AF55" s="2" t="n">
+      <c r="AD55" s="2" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -6428,21 +6094,15 @@
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>0.03386244550347328</v>
       </c>
       <c r="AC56" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0.03248533979058266</v>
-      </c>
-      <c r="AE56" t="n">
         <v>-280</v>
       </c>
-      <c r="AF56" s="2" t="n">
+      <c r="AD56" s="2" t="n">
         <v>45738</v>
       </c>
     </row>
@@ -6534,22 +6194,16 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>0.006396274082362652</v>
       </c>
       <c r="AC57" t="n">
-        <v>146</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0.007090762723237276</v>
-      </c>
-      <c r="AE57" t="n">
         <v>-220</v>
       </c>
-      <c r="AF57" s="2" t="n">
-        <v>45882</v>
+      <c r="AD57" s="2" t="n">
+        <v>45865</v>
       </c>
     </row>
     <row r="58">
@@ -6640,21 +6294,15 @@
         <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>0.01120646949857473</v>
       </c>
       <c r="AC58" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0.01194341108202934</v>
-      </c>
-      <c r="AE58" t="n">
         <v>-310</v>
       </c>
-      <c r="AF58" s="2" t="n">
+      <c r="AD58" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6748,22 +6396,16 @@
         <v>2</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>0.03804760426282883</v>
       </c>
       <c r="AC59" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0.03755462542176247</v>
-      </c>
-      <c r="AE59" t="n">
         <v>-310</v>
       </c>
-      <c r="AF59" s="2" t="n">
-        <v>45798</v>
+      <c r="AD59" s="2" t="n">
+        <v>45783</v>
       </c>
     </row>
     <row r="60">
@@ -6854,21 +6496,15 @@
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>0.02088487520813942</v>
       </c>
       <c r="AC60" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0.02642197906970978</v>
-      </c>
-      <c r="AE60" t="n">
         <v>-297</v>
       </c>
-      <c r="AF60" s="2" t="n">
+      <c r="AD60" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -6962,21 +6598,15 @@
         <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>0.008634621277451515</v>
       </c>
       <c r="AC61" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0.01040103286504745</v>
-      </c>
-      <c r="AE61" t="n">
         <v>-310</v>
       </c>
-      <c r="AF61" s="2" t="n">
+      <c r="AD61" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7068,22 +6698,16 @@
         <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>0.02998095937073231</v>
       </c>
       <c r="AC62" t="n">
-        <v>123</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0.01349372323602438</v>
-      </c>
-      <c r="AE62" t="n">
         <v>-310</v>
       </c>
-      <c r="AF62" s="2" t="n">
-        <v>45951</v>
+      <c r="AD62" s="2" t="n">
+        <v>45921</v>
       </c>
     </row>
     <row r="63">
@@ -7174,21 +6798,15 @@
         <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>0.008236323483288288</v>
       </c>
       <c r="AC63" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0.01118039805442095</v>
-      </c>
-      <c r="AE63" t="n">
         <v>-310</v>
       </c>
-      <c r="AF63" s="2" t="n">
+      <c r="AD63" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7282,22 +6900,16 @@
         <v>1</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>0.1262211203575134</v>
       </c>
       <c r="AC64" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0.1216617673635483</v>
-      </c>
-      <c r="AE64" t="n">
         <v>-310</v>
       </c>
-      <c r="AF64" s="2" t="n">
-        <v>45918</v>
+      <c r="AD64" s="2" t="n">
+        <v>45901</v>
       </c>
     </row>
     <row r="65">
@@ -7390,22 +7002,16 @@
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>0.003346272045746446</v>
       </c>
       <c r="AC65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0.003875332185998559</v>
-      </c>
-      <c r="AE65" t="n">
         <v>-310</v>
       </c>
-      <c r="AF65" s="2" t="n">
-        <v>45783</v>
+      <c r="AD65" s="2" t="n">
+        <v>45768</v>
       </c>
     </row>
     <row r="66">
@@ -7496,21 +7102,15 @@
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>0.05450328812003136</v>
       </c>
       <c r="AC66" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0.05354776605963707</v>
-      </c>
-      <c r="AE66" t="n">
         <v>-310</v>
       </c>
-      <c r="AF66" s="2" t="n">
+      <c r="AD66" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7602,21 +7202,15 @@
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>0.02097393572330475</v>
       </c>
       <c r="AC67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0.02591319009661674</v>
-      </c>
-      <c r="AE67" t="n">
         <v>-310</v>
       </c>
-      <c r="AF67" s="2" t="n">
+      <c r="AD67" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7708,22 +7302,16 @@
         <v>1</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>0.1932605057954788</v>
       </c>
       <c r="AC68" t="n">
-        <v>359</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0.1915939599275589</v>
-      </c>
-      <c r="AE68" t="n">
         <v>-310</v>
       </c>
-      <c r="AF68" s="2" t="n">
-        <v>45903</v>
+      <c r="AD68" s="2" t="n">
+        <v>45901</v>
       </c>
     </row>
     <row r="69">
@@ -7814,22 +7402,16 @@
         <v>1</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>0.008459758944809437</v>
       </c>
       <c r="AC69" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0.009199511259794235</v>
-      </c>
-      <c r="AE69" t="n">
         <v>-310</v>
       </c>
-      <c r="AF69" s="2" t="n">
-        <v>45813</v>
+      <c r="AD69" s="2" t="n">
+        <v>45798</v>
       </c>
     </row>
     <row r="70">
@@ -7922,21 +7504,15 @@
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>0.02598106861114502</v>
       </c>
       <c r="AC70" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0.02402550168335438</v>
-      </c>
-      <c r="AE70" t="n">
         <v>-310</v>
       </c>
-      <c r="AF70" s="2" t="n">
+      <c r="AD70" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -8028,21 +7604,15 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>0.007069978397339582</v>
       </c>
       <c r="AC71" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0.007090866565704346</v>
-      </c>
-      <c r="AE71" t="n">
         <v>-310</v>
       </c>
-      <c r="AF71" s="2" t="n">
+      <c r="AD71" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -8136,22 +7706,16 @@
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>0.003880356904119253</v>
       </c>
       <c r="AC72" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0.003820785088464618</v>
-      </c>
-      <c r="AE72" t="n">
         <v>-205</v>
       </c>
-      <c r="AF72" s="2" t="n">
-        <v>45800</v>
+      <c r="AD72" s="2" t="n">
+        <v>45798</v>
       </c>
     </row>
     <row r="73">
@@ -8242,21 +7806,15 @@
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>0.007789158262312412</v>
       </c>
       <c r="AC73" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0.008872806094586849</v>
-      </c>
-      <c r="AE73" t="n">
         <v>-310</v>
       </c>
-      <c r="AF73" s="2" t="n">
+      <c r="AD73" s="2" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -8348,21 +7906,15 @@
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>0.1933077573776245</v>
       </c>
       <c r="AC74" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0.1942048966884613</v>
-      </c>
-      <c r="AE74" t="n">
         <v>-310</v>
       </c>
-      <c r="AF74" s="2" t="n">
+      <c r="AD74" s="2" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -8456,21 +8008,15 @@
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.3333333333333333</v>
+        <v>1453</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>0.1543121188879013</v>
       </c>
       <c r="AC75" t="n">
-        <v>1453</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0.1409570574760437</v>
-      </c>
-      <c r="AE75" t="n">
         <v>1173</v>
       </c>
-      <c r="AF75" s="2" t="n">
+      <c r="AD75" s="2" t="n">
         <v>45711</v>
       </c>
     </row>
@@ -8564,22 +8110,16 @@
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.3333333333333333</v>
+        <v>999</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>0.725042462348938</v>
       </c>
       <c r="AC76" t="n">
-        <v>999</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0.6690725088119507</v>
-      </c>
-      <c r="AE76" t="n">
         <v>718</v>
       </c>
-      <c r="AF76" s="2" t="n">
-        <v>45806</v>
+      <c r="AD76" s="2" t="n">
+        <v>45692</v>
       </c>
     </row>
     <row r="77">
@@ -8672,22 +8212,16 @@
         <v>2</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.3333333333333333</v>
+        <v>381</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>0.1872734725475311</v>
       </c>
       <c r="AC77" t="n">
-        <v>381</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0.1992234587669373</v>
-      </c>
-      <c r="AE77" t="n">
         <v>101</v>
       </c>
-      <c r="AF77" s="2" t="n">
-        <v>45105</v>
+      <c r="AD77" s="2" t="n">
+        <v>45085</v>
       </c>
     </row>
     <row r="78">
@@ -8778,21 +8312,15 @@
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.3333333333333333</v>
+        <v>375</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>0.1011250019073486</v>
       </c>
       <c r="AC78" t="n">
-        <v>375</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0.09268827736377716</v>
-      </c>
-      <c r="AE78" t="n">
         <v>95</v>
       </c>
-      <c r="AF78" s="2" t="n">
+      <c r="AD78" s="2" t="n">
         <v>45114</v>
       </c>
     </row>
@@ -8886,21 +8414,15 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.3333333333333333</v>
+        <v>282</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>0.2297374606132507</v>
       </c>
       <c r="AC79" t="n">
-        <v>282</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0.2408418953418732</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD79" s="2" t="n">
         <v>45176</v>
       </c>
     </row>
@@ -8992,21 +8514,15 @@
         <v>1</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.3333333333333333</v>
+        <v>261</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>0.229924276471138</v>
       </c>
       <c r="AC80" t="n">
-        <v>261</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>0.2225157767534256</v>
-      </c>
-      <c r="AE80" t="n">
         <v>-39</v>
       </c>
-      <c r="AF80" s="2" t="n">
+      <c r="AD80" s="2" t="n">
         <v>45219</v>
       </c>
     </row>
@@ -9098,22 +8614,16 @@
         <v>1</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.3333333333333333</v>
+        <v>247</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>0.2829222083091736</v>
       </c>
       <c r="AC81" t="n">
-        <v>247</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>0.2749627530574799</v>
-      </c>
-      <c r="AE81" t="n">
         <v>-45</v>
       </c>
-      <c r="AF81" s="2" t="n">
-        <v>45225</v>
+      <c r="AD81" s="2" t="n">
+        <v>45221</v>
       </c>
     </row>
     <row r="82">
@@ -9206,22 +8716,16 @@
         <v>1</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.3333333333333333</v>
+        <v>222</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>0.2449307888746262</v>
       </c>
       <c r="AC82" t="n">
-        <v>222</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0.2558905482292175</v>
-      </c>
-      <c r="AE82" t="n">
         <v>-62</v>
       </c>
-      <c r="AF82" s="2" t="n">
-        <v>45238</v>
+      <c r="AD82" s="2" t="n">
+        <v>45236</v>
       </c>
     </row>
     <row r="83">
@@ -9312,21 +8816,15 @@
         <v>1</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>0.03185803815722466</v>
       </c>
       <c r="AC83" t="n">
-        <v>182</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0.03864405304193497</v>
-      </c>
-      <c r="AE83" t="n">
         <v>-118</v>
       </c>
-      <c r="AF83" s="2" t="n">
+      <c r="AD83" s="2" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -9420,22 +8918,16 @@
         <v>3</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>0.0428675152361393</v>
       </c>
       <c r="AC84" t="n">
-        <v>179</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0.04470883682370186</v>
-      </c>
-      <c r="AE84" t="n">
         <v>-121</v>
       </c>
-      <c r="AF84" s="2" t="n">
-        <v>45400</v>
+      <c r="AD84" s="2" t="n">
+        <v>45301</v>
       </c>
     </row>
     <row r="85">
@@ -9526,21 +9018,15 @@
         <v>1</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>0.03007067926228046</v>
       </c>
       <c r="AC85" t="n">
-        <v>178</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>0.03920075297355652</v>
-      </c>
-      <c r="AE85" t="n">
         <v>-122</v>
       </c>
-      <c r="AF85" s="2" t="n">
+      <c r="AD85" s="2" t="n">
         <v>45296</v>
       </c>
     </row>
@@ -9634,21 +9120,15 @@
         <v>1</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>0.009744884446263313</v>
       </c>
       <c r="AC86" t="n">
-        <v>172</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>0.01146524026989937</v>
-      </c>
-      <c r="AE86" t="n">
         <v>-128</v>
       </c>
-      <c r="AF86" s="2" t="n">
+      <c r="AD86" s="2" t="n">
         <v>45304</v>
       </c>
     </row>
@@ -9740,21 +9220,15 @@
         <v>1</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>0.07821837067604065</v>
       </c>
       <c r="AC87" t="n">
-        <v>172</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>0.08621419221162796</v>
-      </c>
-      <c r="AE87" t="n">
         <v>-128</v>
       </c>
-      <c r="AF87" s="2" t="n">
+      <c r="AD87" s="2" t="n">
         <v>45302</v>
       </c>
     </row>
@@ -9848,21 +9322,15 @@
         <v>3</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.25</v>
+        <v>0.003588069695979357</v>
       </c>
       <c r="AC88" t="n">
-        <v>153</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>0.004396884702146053</v>
-      </c>
-      <c r="AE88" t="n">
         <v>-86</v>
       </c>
-      <c r="AF88" s="2" t="n">
+      <c r="AD88" s="2" t="n">
         <v>45266</v>
       </c>
     </row>
@@ -9956,21 +9424,15 @@
         <v>1</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>0.002992108929902315</v>
       </c>
       <c r="AC89" t="n">
-        <v>150</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>0.002825111616402864</v>
-      </c>
-      <c r="AE89" t="n">
         <v>-89</v>
       </c>
-      <c r="AF89" s="2" t="n">
+      <c r="AD89" s="2" t="n">
         <v>45265</v>
       </c>
     </row>
@@ -10064,22 +9526,16 @@
         <v>1</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>0.00426445621997118</v>
       </c>
       <c r="AC90" t="n">
-        <v>149</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>0.00390627421438694</v>
-      </c>
-      <c r="AE90" t="n">
         <v>-90</v>
       </c>
-      <c r="AF90" s="2" t="n">
-        <v>45267</v>
+      <c r="AD90" s="2" t="n">
+        <v>45236</v>
       </c>
     </row>
     <row r="91">
@@ -10170,21 +9626,15 @@
         <v>1</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>0.01308925729244947</v>
       </c>
       <c r="AC91" t="n">
-        <v>139</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0.009338484145700932</v>
-      </c>
-      <c r="AE91" t="n">
         <v>-130</v>
       </c>
-      <c r="AF91" s="2" t="n">
+      <c r="AD91" s="2" t="n">
         <v>45304</v>
       </c>
     </row>
@@ -10276,21 +9726,15 @@
         <v>1</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>0.01405024435371161</v>
       </c>
       <c r="AC92" t="n">
-        <v>128</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>0.01252417452633381</v>
-      </c>
-      <c r="AE92" t="n">
         <v>-141</v>
       </c>
-      <c r="AF92" s="2" t="n">
+      <c r="AD92" s="2" t="n">
         <v>45315</v>
       </c>
     </row>
@@ -10382,22 +9826,16 @@
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>0.006367234978824854</v>
       </c>
       <c r="AC93" t="n">
-        <v>128</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0.00579608790576458</v>
-      </c>
-      <c r="AE93" t="n">
         <v>-141</v>
       </c>
-      <c r="AF93" s="2" t="n">
-        <v>45317</v>
+      <c r="AD93" s="2" t="n">
+        <v>45315</v>
       </c>
     </row>
     <row r="94">
@@ -10488,21 +9926,15 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>0.01228058431297541</v>
       </c>
       <c r="AC94" t="n">
-        <v>110</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0.01023478712886572</v>
-      </c>
-      <c r="AE94" t="n">
         <v>-130</v>
       </c>
-      <c r="AF94" s="2" t="n">
+      <c r="AD94" s="2" t="n">
         <v>45273</v>
       </c>
     </row>
@@ -10596,21 +10028,15 @@
         <v>1</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>0.01142765954136848</v>
       </c>
       <c r="AC95" t="n">
-        <v>96</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>0.00821247324347496</v>
-      </c>
-      <c r="AE95" t="n">
         <v>-144</v>
       </c>
-      <c r="AF95" s="2" t="n">
+      <c r="AD95" s="2" t="n">
         <v>45318</v>
       </c>
     </row>
@@ -10702,22 +10128,16 @@
         <v>1</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>0.01021143049001694</v>
       </c>
       <c r="AC96" t="n">
-        <v>93</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0.009250856935977936</v>
-      </c>
-      <c r="AE96" t="n">
         <v>-147</v>
       </c>
-      <c r="AF96" s="2" t="n">
-        <v>45324</v>
+      <c r="AD96" s="2" t="n">
+        <v>45293</v>
       </c>
     </row>
     <row r="97">
@@ -10810,22 +10230,16 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>0.01594741456210613</v>
       </c>
       <c r="AC97" t="n">
-        <v>92</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>0.01411768142133951</v>
-      </c>
-      <c r="AE97" t="n">
         <v>-148</v>
       </c>
-      <c r="AF97" s="2" t="n">
-        <v>45294</v>
+      <c r="AD97" s="2" t="n">
+        <v>45293</v>
       </c>
     </row>
     <row r="98">
@@ -10918,21 +10332,15 @@
         <v>1</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>0.004730436485260725</v>
       </c>
       <c r="AC98" t="n">
-        <v>86</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>0.005402962677180767</v>
-      </c>
-      <c r="AE98" t="n">
         <v>-185</v>
       </c>
-      <c r="AF98" s="2" t="n">
+      <c r="AD98" s="2" t="n">
         <v>45359</v>
       </c>
     </row>
